--- a/旭土地_保険一覧.xlsx
+++ b/旭土地_保険一覧.xlsx
@@ -3765,13 +3765,166 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
+      <t xml:space="preserve">来期計
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(R8/10</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">〜</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">R9/9)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">保険料 現金支払計</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="10"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">※来期計は令和</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="10"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">8</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="10"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="10"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="10"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月〜令和</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="10"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">9</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="10"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="10"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">9</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="10"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="10"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="10"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
       <t xml:space="preserve">令和</t>
     </r>
     <r>
       <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FFFFFFFF"/>
+        <i val="true"/>
+        <sz val="10"/>
+        <color rgb="FF595959"/>
         <rFont val="Arial"/>
         <family val="0"/>
         <charset val="1"/>
@@ -3780,61 +3933,13 @@
     </r>
     <r>
       <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">年度計
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(R9/4</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">〜</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">R10/3)</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">保険料 現金支払計</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <i val="true"/>
-        <sz val="10"/>
-        <color rgb="FF595959"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">※令和</t>
+        <i val="true"/>
+        <sz val="10"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年</t>
     </r>
     <r>
       <rPr>
@@ -3855,133 +3960,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">年度計は暦の令和</t>
-    </r>
-    <r>
-      <rPr>
-        <i val="true"/>
-        <sz val="10"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">9</t>
-    </r>
-    <r>
-      <rPr>
-        <i val="true"/>
-        <sz val="10"/>
-        <color rgb="FF595959"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">年</t>
-    </r>
-    <r>
-      <rPr>
-        <i val="true"/>
-        <sz val="10"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">4</t>
-    </r>
-    <r>
-      <rPr>
-        <i val="true"/>
-        <sz val="10"/>
-        <color rgb="FF595959"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">月〜令和</t>
-    </r>
-    <r>
-      <rPr>
-        <i val="true"/>
-        <sz val="10"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">10</t>
-    </r>
-    <r>
-      <rPr>
-        <i val="true"/>
-        <sz val="10"/>
-        <color rgb="FF595959"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">年</t>
-    </r>
-    <r>
-      <rPr>
-        <i val="true"/>
-        <sz val="10"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">3</t>
-    </r>
-    <r>
-      <rPr>
-        <i val="true"/>
-        <sz val="10"/>
-        <color rgb="FF595959"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">月の合計。カレンダー範囲外の月は含まれません</t>
-    </r>
-    <r>
-      <rPr>
-        <i val="true"/>
-        <sz val="10"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <i val="true"/>
-        <sz val="10"/>
-        <color rgb="FF595959"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">初月は</t>
-    </r>
-    <r>
-      <rPr>
-        <i val="true"/>
-        <sz val="10"/>
-        <color rgb="FF595959"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">4</t>
-    </r>
-    <r>
-      <rPr>
-        <i val="true"/>
-        <sz val="10"/>
-        <color rgb="FF595959"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">行目の黄色でなく先頭セルの日付で変更可</t>
+      <t xml:space="preserve">月期</t>
     </r>
     <r>
       <rPr>
@@ -4002,7 +3981,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">。</t>
+      <t xml:space="preserve">の合計。年払の支払月は加入日の月と仮定しています。</t>
     </r>
   </si>
 </sst>
@@ -7175,14 +7154,14 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:V28"/>
+  <dimension ref="A1:P28"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="3" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="3" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="14"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7247,34 +7226,10 @@
         <f aca="false">EDATE(M4,1)</f>
         <v>46631</v>
       </c>
-      <c r="O4" s="32" t="n">
-        <f aca="false">EDATE(N4,1)</f>
-        <v>46661</v>
-      </c>
-      <c r="P4" s="32" t="n">
-        <f aca="false">EDATE(O4,1)</f>
-        <v>46692</v>
-      </c>
-      <c r="Q4" s="32" t="n">
-        <f aca="false">EDATE(P4,1)</f>
-        <v>46722</v>
-      </c>
-      <c r="R4" s="32" t="n">
-        <f aca="false">EDATE(Q4,1)</f>
-        <v>46753</v>
-      </c>
-      <c r="S4" s="32" t="n">
-        <f aca="false">EDATE(R4,1)</f>
-        <v>46784</v>
-      </c>
-      <c r="T4" s="32" t="n">
-        <f aca="false">EDATE(S4,1)</f>
-        <v>46813</v>
-      </c>
-      <c r="U4" s="3" t="s">
+      <c r="O4" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="V4" s="3" t="s">
+      <c r="P4" s="3" t="s">
         <v>133</v>
       </c>
     </row>
@@ -7332,36 +7287,12 @@
         <f aca="false">IF(OR(保険一覧!$S5="",N$4&lt;保険一覧!$S5),IF(保険一覧!$J5="月払",保険一覧!$K5,IF(AND(保険一覧!$J5="年払",MONTH(N$4)=保険一覧!$R5),保険一覧!$K5,0)),0)</f>
         <v>0</v>
       </c>
-      <c r="O6" s="34" t="n">
-        <f aca="false">IF(OR(保険一覧!$S5="",O$4&lt;保険一覧!$S5),IF(保険一覧!$J5="月払",保険一覧!$K5,IF(AND(保険一覧!$J5="年払",MONTH(O$4)=保険一覧!$R5),保険一覧!$K5,0)),0)</f>
-        <v>0</v>
-      </c>
-      <c r="P6" s="34" t="n">
-        <f aca="false">IF(OR(保険一覧!$S5="",P$4&lt;保険一覧!$S5),IF(保険一覧!$J5="月払",保険一覧!$K5,IF(AND(保険一覧!$J5="年払",MONTH(P$4)=保険一覧!$R5),保険一覧!$K5,0)),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q6" s="34" t="n">
-        <f aca="false">IF(OR(保険一覧!$S5="",Q$4&lt;保険一覧!$S5),IF(保険一覧!$J5="月払",保険一覧!$K5,IF(AND(保険一覧!$J5="年払",MONTH(Q$4)=保険一覧!$R5),保険一覧!$K5,0)),0)</f>
-        <v>0</v>
-      </c>
-      <c r="R6" s="34" t="n">
-        <f aca="false">IF(OR(保険一覧!$S5="",R$4&lt;保険一覧!$S5),IF(保険一覧!$J5="月払",保険一覧!$K5,IF(AND(保険一覧!$J5="年払",MONTH(R$4)=保険一覧!$R5),保険一覧!$K5,0)),0)</f>
-        <v>0</v>
-      </c>
-      <c r="S6" s="34" t="n">
-        <f aca="false">IF(OR(保険一覧!$S5="",S$4&lt;保険一覧!$S5),IF(保険一覧!$J5="月払",保険一覧!$K5,IF(AND(保険一覧!$J5="年払",MONTH(S$4)=保険一覧!$R5),保険一覧!$K5,0)),0)</f>
-        <v>0</v>
-      </c>
-      <c r="T6" s="34" t="n">
-        <f aca="false">IF(OR(保険一覧!$S5="",T$4&lt;保険一覧!$S5),IF(保険一覧!$J5="月払",保険一覧!$K5,IF(AND(保険一覧!$J5="年払",MONTH(T$4)=保険一覧!$R5),保険一覧!$K5,0)),0)</f>
-        <v>0</v>
-      </c>
-      <c r="U6" s="10" t="n">
-        <f aca="false">SUM(C6:T6)</f>
-        <v>0</v>
-      </c>
-      <c r="V6" s="10" t="n">
-        <f aca="false">SUMIFS(C6:T6,$C$4:$T$4,"&gt;="&amp;DATE(2027,4,1),$C$4:$T$4,"&lt;="&amp;DATE(2028,3,1))</f>
+      <c r="O6" s="10" t="n">
+        <f aca="false">SUM(C6:N6)</f>
+        <v>0</v>
+      </c>
+      <c r="P6" s="10" t="n">
+        <f aca="false">SUMIFS(C6:N6,$C$4:$N$4,"&gt;="&amp;DATE(2026,10,1),$C$4:$N$4,"&lt;="&amp;DATE(2027,9,1))</f>
         <v>0</v>
       </c>
     </row>
@@ -7419,36 +7350,12 @@
         <f aca="false">IF(OR(保険一覧!$S6="",N$4&lt;保険一覧!$S6),IF(保険一覧!$J6="月払",保険一覧!$K6,IF(AND(保険一覧!$J6="年払",MONTH(N$4)=保険一覧!$R6),保険一覧!$K6,0)),0)</f>
         <v>0</v>
       </c>
-      <c r="O7" s="34" t="n">
-        <f aca="false">IF(OR(保険一覧!$S6="",O$4&lt;保険一覧!$S6),IF(保険一覧!$J6="月払",保険一覧!$K6,IF(AND(保険一覧!$J6="年払",MONTH(O$4)=保険一覧!$R6),保険一覧!$K6,0)),0)</f>
-        <v>0</v>
-      </c>
-      <c r="P7" s="34" t="n">
-        <f aca="false">IF(OR(保険一覧!$S6="",P$4&lt;保険一覧!$S6),IF(保険一覧!$J6="月払",保険一覧!$K6,IF(AND(保険一覧!$J6="年払",MONTH(P$4)=保険一覧!$R6),保険一覧!$K6,0)),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q7" s="34" t="n">
-        <f aca="false">IF(OR(保険一覧!$S6="",Q$4&lt;保険一覧!$S6),IF(保険一覧!$J6="月払",保険一覧!$K6,IF(AND(保険一覧!$J6="年払",MONTH(Q$4)=保険一覧!$R6),保険一覧!$K6,0)),0)</f>
-        <v>0</v>
-      </c>
-      <c r="R7" s="34" t="n">
-        <f aca="false">IF(OR(保険一覧!$S6="",R$4&lt;保険一覧!$S6),IF(保険一覧!$J6="月払",保険一覧!$K6,IF(AND(保険一覧!$J6="年払",MONTH(R$4)=保険一覧!$R6),保険一覧!$K6,0)),0)</f>
-        <v>0</v>
-      </c>
-      <c r="S7" s="34" t="n">
-        <f aca="false">IF(OR(保険一覧!$S6="",S$4&lt;保険一覧!$S6),IF(保険一覧!$J6="月払",保険一覧!$K6,IF(AND(保険一覧!$J6="年払",MONTH(S$4)=保険一覧!$R6),保険一覧!$K6,0)),0)</f>
-        <v>0</v>
-      </c>
-      <c r="T7" s="34" t="n">
-        <f aca="false">IF(OR(保険一覧!$S6="",T$4&lt;保険一覧!$S6),IF(保険一覧!$J6="月払",保険一覧!$K6,IF(AND(保険一覧!$J6="年払",MONTH(T$4)=保険一覧!$R6),保険一覧!$K6,0)),0)</f>
-        <v>0</v>
-      </c>
-      <c r="U7" s="10" t="n">
-        <f aca="false">SUM(C7:T7)</f>
-        <v>0</v>
-      </c>
-      <c r="V7" s="10" t="n">
-        <f aca="false">SUMIFS(C7:T7,$C$4:$T$4,"&gt;="&amp;DATE(2027,4,1),$C$4:$T$4,"&lt;="&amp;DATE(2028,3,1))</f>
+      <c r="O7" s="10" t="n">
+        <f aca="false">SUM(C7:N7)</f>
+        <v>0</v>
+      </c>
+      <c r="P7" s="10" t="n">
+        <f aca="false">SUMIFS(C7:N7,$C$4:$N$4,"&gt;="&amp;DATE(2026,10,1),$C$4:$N$4,"&lt;="&amp;DATE(2027,9,1))</f>
         <v>0</v>
       </c>
     </row>
@@ -7506,36 +7413,12 @@
         <f aca="false">IF(OR(保険一覧!$S7="",N$4&lt;保険一覧!$S7),IF(保険一覧!$J7="月払",保険一覧!$K7,IF(AND(保険一覧!$J7="年払",MONTH(N$4)=保険一覧!$R7),保険一覧!$K7,0)),0)</f>
         <v>0</v>
       </c>
-      <c r="O8" s="34" t="n">
-        <f aca="false">IF(OR(保険一覧!$S7="",O$4&lt;保険一覧!$S7),IF(保険一覧!$J7="月払",保険一覧!$K7,IF(AND(保険一覧!$J7="年払",MONTH(O$4)=保険一覧!$R7),保険一覧!$K7,0)),0)</f>
-        <v>0</v>
-      </c>
-      <c r="P8" s="34" t="n">
-        <f aca="false">IF(OR(保険一覧!$S7="",P$4&lt;保険一覧!$S7),IF(保険一覧!$J7="月払",保険一覧!$K7,IF(AND(保険一覧!$J7="年払",MONTH(P$4)=保険一覧!$R7),保険一覧!$K7,0)),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q8" s="34" t="n">
-        <f aca="false">IF(OR(保険一覧!$S7="",Q$4&lt;保険一覧!$S7),IF(保険一覧!$J7="月払",保険一覧!$K7,IF(AND(保険一覧!$J7="年払",MONTH(Q$4)=保険一覧!$R7),保険一覧!$K7,0)),0)</f>
-        <v>0</v>
-      </c>
-      <c r="R8" s="34" t="n">
-        <f aca="false">IF(OR(保険一覧!$S7="",R$4&lt;保険一覧!$S7),IF(保険一覧!$J7="月払",保険一覧!$K7,IF(AND(保険一覧!$J7="年払",MONTH(R$4)=保険一覧!$R7),保険一覧!$K7,0)),0)</f>
-        <v>0</v>
-      </c>
-      <c r="S8" s="34" t="n">
-        <f aca="false">IF(OR(保険一覧!$S7="",S$4&lt;保険一覧!$S7),IF(保険一覧!$J7="月払",保険一覧!$K7,IF(AND(保険一覧!$J7="年払",MONTH(S$4)=保険一覧!$R7),保険一覧!$K7,0)),0)</f>
-        <v>0</v>
-      </c>
-      <c r="T8" s="34" t="n">
-        <f aca="false">IF(OR(保険一覧!$S7="",T$4&lt;保険一覧!$S7),IF(保険一覧!$J7="月払",保険一覧!$K7,IF(AND(保険一覧!$J7="年払",MONTH(T$4)=保険一覧!$R7),保険一覧!$K7,0)),0)</f>
-        <v>0</v>
-      </c>
-      <c r="U8" s="10" t="n">
-        <f aca="false">SUM(C8:T8)</f>
-        <v>0</v>
-      </c>
-      <c r="V8" s="10" t="n">
-        <f aca="false">SUMIFS(C8:T8,$C$4:$T$4,"&gt;="&amp;DATE(2027,4,1),$C$4:$T$4,"&lt;="&amp;DATE(2028,3,1))</f>
+      <c r="O8" s="10" t="n">
+        <f aca="false">SUM(C8:N8)</f>
+        <v>0</v>
+      </c>
+      <c r="P8" s="10" t="n">
+        <f aca="false">SUMIFS(C8:N8,$C$4:$N$4,"&gt;="&amp;DATE(2026,10,1),$C$4:$N$4,"&lt;="&amp;DATE(2027,9,1))</f>
         <v>0</v>
       </c>
     </row>
@@ -7593,36 +7476,12 @@
         <f aca="false">IF(OR(保険一覧!$S8="",N$4&lt;保険一覧!$S8),IF(保険一覧!$J8="月払",保険一覧!$K8,IF(AND(保険一覧!$J8="年払",MONTH(N$4)=保険一覧!$R8),保険一覧!$K8,0)),0)</f>
         <v>0</v>
       </c>
-      <c r="O9" s="34" t="n">
-        <f aca="false">IF(OR(保険一覧!$S8="",O$4&lt;保険一覧!$S8),IF(保険一覧!$J8="月払",保険一覧!$K8,IF(AND(保険一覧!$J8="年払",MONTH(O$4)=保険一覧!$R8),保険一覧!$K8,0)),0)</f>
-        <v>0</v>
-      </c>
-      <c r="P9" s="34" t="n">
-        <f aca="false">IF(OR(保険一覧!$S8="",P$4&lt;保険一覧!$S8),IF(保険一覧!$J8="月払",保険一覧!$K8,IF(AND(保険一覧!$J8="年払",MONTH(P$4)=保険一覧!$R8),保険一覧!$K8,0)),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q9" s="34" t="n">
-        <f aca="false">IF(OR(保険一覧!$S8="",Q$4&lt;保険一覧!$S8),IF(保険一覧!$J8="月払",保険一覧!$K8,IF(AND(保険一覧!$J8="年払",MONTH(Q$4)=保険一覧!$R8),保険一覧!$K8,0)),0)</f>
-        <v>0</v>
-      </c>
-      <c r="R9" s="34" t="n">
-        <f aca="false">IF(OR(保険一覧!$S8="",R$4&lt;保険一覧!$S8),IF(保険一覧!$J8="月払",保険一覧!$K8,IF(AND(保険一覧!$J8="年払",MONTH(R$4)=保険一覧!$R8),保険一覧!$K8,0)),0)</f>
-        <v>0</v>
-      </c>
-      <c r="S9" s="34" t="n">
-        <f aca="false">IF(OR(保険一覧!$S8="",S$4&lt;保険一覧!$S8),IF(保険一覧!$J8="月払",保険一覧!$K8,IF(AND(保険一覧!$J8="年払",MONTH(S$4)=保険一覧!$R8),保険一覧!$K8,0)),0)</f>
-        <v>0</v>
-      </c>
-      <c r="T9" s="34" t="n">
-        <f aca="false">IF(OR(保険一覧!$S8="",T$4&lt;保険一覧!$S8),IF(保険一覧!$J8="月払",保険一覧!$K8,IF(AND(保険一覧!$J8="年払",MONTH(T$4)=保険一覧!$R8),保険一覧!$K8,0)),0)</f>
-        <v>0</v>
-      </c>
-      <c r="U9" s="10" t="n">
-        <f aca="false">SUM(C9:T9)</f>
-        <v>0</v>
-      </c>
-      <c r="V9" s="10" t="n">
-        <f aca="false">SUMIFS(C9:T9,$C$4:$T$4,"&gt;="&amp;DATE(2027,4,1),$C$4:$T$4,"&lt;="&amp;DATE(2028,3,1))</f>
+      <c r="O9" s="10" t="n">
+        <f aca="false">SUM(C9:N9)</f>
+        <v>0</v>
+      </c>
+      <c r="P9" s="10" t="n">
+        <f aca="false">SUMIFS(C9:N9,$C$4:$N$4,"&gt;="&amp;DATE(2026,10,1),$C$4:$N$4,"&lt;="&amp;DATE(2027,9,1))</f>
         <v>0</v>
       </c>
     </row>
@@ -7680,36 +7539,12 @@
         <f aca="false">IF(OR(保険一覧!$S9="",N$4&lt;保険一覧!$S9),IF(保険一覧!$J9="月払",保険一覧!$K9,IF(AND(保険一覧!$J9="年払",MONTH(N$4)=保険一覧!$R9),保険一覧!$K9,0)),0)</f>
         <v>22820</v>
       </c>
-      <c r="O10" s="34" t="n">
-        <f aca="false">IF(OR(保険一覧!$S9="",O$4&lt;保険一覧!$S9),IF(保険一覧!$J9="月払",保険一覧!$K9,IF(AND(保険一覧!$J9="年払",MONTH(O$4)=保険一覧!$R9),保険一覧!$K9,0)),0)</f>
-        <v>22820</v>
-      </c>
-      <c r="P10" s="34" t="n">
-        <f aca="false">IF(OR(保険一覧!$S9="",P$4&lt;保険一覧!$S9),IF(保険一覧!$J9="月払",保険一覧!$K9,IF(AND(保険一覧!$J9="年払",MONTH(P$4)=保険一覧!$R9),保険一覧!$K9,0)),0)</f>
-        <v>22820</v>
-      </c>
-      <c r="Q10" s="34" t="n">
-        <f aca="false">IF(OR(保険一覧!$S9="",Q$4&lt;保険一覧!$S9),IF(保険一覧!$J9="月払",保険一覧!$K9,IF(AND(保険一覧!$J9="年払",MONTH(Q$4)=保険一覧!$R9),保険一覧!$K9,0)),0)</f>
-        <v>22820</v>
-      </c>
-      <c r="R10" s="34" t="n">
-        <f aca="false">IF(OR(保険一覧!$S9="",R$4&lt;保険一覧!$S9),IF(保険一覧!$J9="月払",保険一覧!$K9,IF(AND(保険一覧!$J9="年払",MONTH(R$4)=保険一覧!$R9),保険一覧!$K9,0)),0)</f>
-        <v>22820</v>
-      </c>
-      <c r="S10" s="34" t="n">
-        <f aca="false">IF(OR(保険一覧!$S9="",S$4&lt;保険一覧!$S9),IF(保険一覧!$J9="月払",保険一覧!$K9,IF(AND(保険一覧!$J9="年払",MONTH(S$4)=保険一覧!$R9),保険一覧!$K9,0)),0)</f>
-        <v>22820</v>
-      </c>
-      <c r="T10" s="34" t="n">
-        <f aca="false">IF(OR(保険一覧!$S9="",T$4&lt;保険一覧!$S9),IF(保険一覧!$J9="月払",保険一覧!$K9,IF(AND(保険一覧!$J9="年払",MONTH(T$4)=保険一覧!$R9),保険一覧!$K9,0)),0)</f>
-        <v>22820</v>
-      </c>
-      <c r="U10" s="10" t="n">
-        <f aca="false">SUM(C10:T10)</f>
-        <v>410760</v>
-      </c>
-      <c r="V10" s="10" t="n">
-        <f aca="false">SUMIFS(C10:T10,$C$4:$T$4,"&gt;="&amp;DATE(2027,4,1),$C$4:$T$4,"&lt;="&amp;DATE(2028,3,1))</f>
+      <c r="O10" s="10" t="n">
+        <f aca="false">SUM(C10:N10)</f>
+        <v>273840</v>
+      </c>
+      <c r="P10" s="10" t="n">
+        <f aca="false">SUMIFS(C10:N10,$C$4:$N$4,"&gt;="&amp;DATE(2026,10,1),$C$4:$N$4,"&lt;="&amp;DATE(2027,9,1))</f>
         <v>273840</v>
       </c>
     </row>
@@ -7767,36 +7602,12 @@
         <f aca="false">IF(OR(保険一覧!$S10="",N$4&lt;保険一覧!$S10),IF(保険一覧!$J10="月払",保険一覧!$K10,IF(AND(保険一覧!$J10="年払",MONTH(N$4)=保険一覧!$R10),保険一覧!$K10,0)),0)</f>
         <v>49130</v>
       </c>
-      <c r="O11" s="34" t="n">
-        <f aca="false">IF(OR(保険一覧!$S10="",O$4&lt;保険一覧!$S10),IF(保険一覧!$J10="月払",保険一覧!$K10,IF(AND(保険一覧!$J10="年払",MONTH(O$4)=保険一覧!$R10),保険一覧!$K10,0)),0)</f>
-        <v>49130</v>
-      </c>
-      <c r="P11" s="34" t="n">
-        <f aca="false">IF(OR(保険一覧!$S10="",P$4&lt;保険一覧!$S10),IF(保険一覧!$J10="月払",保険一覧!$K10,IF(AND(保険一覧!$J10="年払",MONTH(P$4)=保険一覧!$R10),保険一覧!$K10,0)),0)</f>
-        <v>49130</v>
-      </c>
-      <c r="Q11" s="34" t="n">
-        <f aca="false">IF(OR(保険一覧!$S10="",Q$4&lt;保険一覧!$S10),IF(保険一覧!$J10="月払",保険一覧!$K10,IF(AND(保険一覧!$J10="年払",MONTH(Q$4)=保険一覧!$R10),保険一覧!$K10,0)),0)</f>
-        <v>49130</v>
-      </c>
-      <c r="R11" s="34" t="n">
-        <f aca="false">IF(OR(保険一覧!$S10="",R$4&lt;保険一覧!$S10),IF(保険一覧!$J10="月払",保険一覧!$K10,IF(AND(保険一覧!$J10="年払",MONTH(R$4)=保険一覧!$R10),保険一覧!$K10,0)),0)</f>
-        <v>49130</v>
-      </c>
-      <c r="S11" s="34" t="n">
-        <f aca="false">IF(OR(保険一覧!$S10="",S$4&lt;保険一覧!$S10),IF(保険一覧!$J10="月払",保険一覧!$K10,IF(AND(保険一覧!$J10="年払",MONTH(S$4)=保険一覧!$R10),保険一覧!$K10,0)),0)</f>
-        <v>49130</v>
-      </c>
-      <c r="T11" s="34" t="n">
-        <f aca="false">IF(OR(保険一覧!$S10="",T$4&lt;保険一覧!$S10),IF(保険一覧!$J10="月払",保険一覧!$K10,IF(AND(保険一覧!$J10="年払",MONTH(T$4)=保険一覧!$R10),保険一覧!$K10,0)),0)</f>
-        <v>49130</v>
-      </c>
-      <c r="U11" s="10" t="n">
-        <f aca="false">SUM(C11:T11)</f>
-        <v>884340</v>
-      </c>
-      <c r="V11" s="10" t="n">
-        <f aca="false">SUMIFS(C11:T11,$C$4:$T$4,"&gt;="&amp;DATE(2027,4,1),$C$4:$T$4,"&lt;="&amp;DATE(2028,3,1))</f>
+      <c r="O11" s="10" t="n">
+        <f aca="false">SUM(C11:N11)</f>
+        <v>589560</v>
+      </c>
+      <c r="P11" s="10" t="n">
+        <f aca="false">SUMIFS(C11:N11,$C$4:$N$4,"&gt;="&amp;DATE(2026,10,1),$C$4:$N$4,"&lt;="&amp;DATE(2027,9,1))</f>
         <v>589560</v>
       </c>
     </row>
@@ -7854,36 +7665,12 @@
         <f aca="false">IF(OR(保険一覧!$S11="",N$4&lt;保険一覧!$S11),IF(保険一覧!$J11="月払",保険一覧!$K11,IF(AND(保険一覧!$J11="年払",MONTH(N$4)=保険一覧!$R11),保険一覧!$K11,0)),0)</f>
         <v>505120</v>
       </c>
-      <c r="O12" s="34" t="n">
-        <f aca="false">IF(OR(保険一覧!$S11="",O$4&lt;保険一覧!$S11),IF(保険一覧!$J11="月払",保険一覧!$K11,IF(AND(保険一覧!$J11="年払",MONTH(O$4)=保険一覧!$R11),保険一覧!$K11,0)),0)</f>
-        <v>505120</v>
-      </c>
-      <c r="P12" s="34" t="n">
-        <f aca="false">IF(OR(保険一覧!$S11="",P$4&lt;保険一覧!$S11),IF(保険一覧!$J11="月払",保険一覧!$K11,IF(AND(保険一覧!$J11="年払",MONTH(P$4)=保険一覧!$R11),保険一覧!$K11,0)),0)</f>
-        <v>505120</v>
-      </c>
-      <c r="Q12" s="34" t="n">
-        <f aca="false">IF(OR(保険一覧!$S11="",Q$4&lt;保険一覧!$S11),IF(保険一覧!$J11="月払",保険一覧!$K11,IF(AND(保険一覧!$J11="年払",MONTH(Q$4)=保険一覧!$R11),保険一覧!$K11,0)),0)</f>
-        <v>505120</v>
-      </c>
-      <c r="R12" s="34" t="n">
-        <f aca="false">IF(OR(保険一覧!$S11="",R$4&lt;保険一覧!$S11),IF(保険一覧!$J11="月払",保険一覧!$K11,IF(AND(保険一覧!$J11="年払",MONTH(R$4)=保険一覧!$R11),保険一覧!$K11,0)),0)</f>
-        <v>505120</v>
-      </c>
-      <c r="S12" s="34" t="n">
-        <f aca="false">IF(OR(保険一覧!$S11="",S$4&lt;保険一覧!$S11),IF(保険一覧!$J11="月払",保険一覧!$K11,IF(AND(保険一覧!$J11="年払",MONTH(S$4)=保険一覧!$R11),保険一覧!$K11,0)),0)</f>
-        <v>505120</v>
-      </c>
-      <c r="T12" s="34" t="n">
-        <f aca="false">IF(OR(保険一覧!$S11="",T$4&lt;保険一覧!$S11),IF(保険一覧!$J11="月払",保険一覧!$K11,IF(AND(保険一覧!$J11="年払",MONTH(T$4)=保険一覧!$R11),保険一覧!$K11,0)),0)</f>
-        <v>505120</v>
-      </c>
-      <c r="U12" s="10" t="n">
-        <f aca="false">SUM(C12:T12)</f>
-        <v>9092160</v>
-      </c>
-      <c r="V12" s="10" t="n">
-        <f aca="false">SUMIFS(C12:T12,$C$4:$T$4,"&gt;="&amp;DATE(2027,4,1),$C$4:$T$4,"&lt;="&amp;DATE(2028,3,1))</f>
+      <c r="O12" s="10" t="n">
+        <f aca="false">SUM(C12:N12)</f>
+        <v>6061440</v>
+      </c>
+      <c r="P12" s="10" t="n">
+        <f aca="false">SUMIFS(C12:N12,$C$4:$N$4,"&gt;="&amp;DATE(2026,10,1),$C$4:$N$4,"&lt;="&amp;DATE(2027,9,1))</f>
         <v>6061440</v>
       </c>
     </row>
@@ -7941,36 +7728,12 @@
         <f aca="false">IF(OR(保険一覧!$S12="",N$4&lt;保険一覧!$S12),IF(保険一覧!$J12="月払",保険一覧!$K12,IF(AND(保険一覧!$J12="年払",MONTH(N$4)=保険一覧!$R12),保険一覧!$K12,0)),0)</f>
         <v>57687</v>
       </c>
-      <c r="O13" s="34" t="n">
-        <f aca="false">IF(OR(保険一覧!$S12="",O$4&lt;保険一覧!$S12),IF(保険一覧!$J12="月払",保険一覧!$K12,IF(AND(保険一覧!$J12="年払",MONTH(O$4)=保険一覧!$R12),保険一覧!$K12,0)),0)</f>
-        <v>57687</v>
-      </c>
-      <c r="P13" s="34" t="n">
-        <f aca="false">IF(OR(保険一覧!$S12="",P$4&lt;保険一覧!$S12),IF(保険一覧!$J12="月払",保険一覧!$K12,IF(AND(保険一覧!$J12="年払",MONTH(P$4)=保険一覧!$R12),保険一覧!$K12,0)),0)</f>
-        <v>57687</v>
-      </c>
-      <c r="Q13" s="34" t="n">
-        <f aca="false">IF(OR(保険一覧!$S12="",Q$4&lt;保険一覧!$S12),IF(保険一覧!$J12="月払",保険一覧!$K12,IF(AND(保険一覧!$J12="年払",MONTH(Q$4)=保険一覧!$R12),保険一覧!$K12,0)),0)</f>
-        <v>57687</v>
-      </c>
-      <c r="R13" s="34" t="n">
-        <f aca="false">IF(OR(保険一覧!$S12="",R$4&lt;保険一覧!$S12),IF(保険一覧!$J12="月払",保険一覧!$K12,IF(AND(保険一覧!$J12="年払",MONTH(R$4)=保険一覧!$R12),保険一覧!$K12,0)),0)</f>
-        <v>57687</v>
-      </c>
-      <c r="S13" s="34" t="n">
-        <f aca="false">IF(OR(保険一覧!$S12="",S$4&lt;保険一覧!$S12),IF(保険一覧!$J12="月払",保険一覧!$K12,IF(AND(保険一覧!$J12="年払",MONTH(S$4)=保険一覧!$R12),保険一覧!$K12,0)),0)</f>
-        <v>57687</v>
-      </c>
-      <c r="T13" s="34" t="n">
-        <f aca="false">IF(OR(保険一覧!$S12="",T$4&lt;保険一覧!$S12),IF(保険一覧!$J12="月払",保険一覧!$K12,IF(AND(保険一覧!$J12="年払",MONTH(T$4)=保険一覧!$R12),保険一覧!$K12,0)),0)</f>
-        <v>57687</v>
-      </c>
-      <c r="U13" s="10" t="n">
-        <f aca="false">SUM(C13:T13)</f>
-        <v>1038366</v>
-      </c>
-      <c r="V13" s="10" t="n">
-        <f aca="false">SUMIFS(C13:T13,$C$4:$T$4,"&gt;="&amp;DATE(2027,4,1),$C$4:$T$4,"&lt;="&amp;DATE(2028,3,1))</f>
+      <c r="O13" s="10" t="n">
+        <f aca="false">SUM(C13:N13)</f>
+        <v>692244</v>
+      </c>
+      <c r="P13" s="10" t="n">
+        <f aca="false">SUMIFS(C13:N13,$C$4:$N$4,"&gt;="&amp;DATE(2026,10,1),$C$4:$N$4,"&lt;="&amp;DATE(2027,9,1))</f>
         <v>692244</v>
       </c>
     </row>
@@ -8028,36 +7791,12 @@
         <f aca="false">IF(OR(保険一覧!$S13="",N$4&lt;保険一覧!$S13),IF(保険一覧!$J13="月払",保険一覧!$K13,IF(AND(保険一覧!$J13="年払",MONTH(N$4)=保険一覧!$R13),保険一覧!$K13,0)),0)</f>
         <v>179573</v>
       </c>
-      <c r="O14" s="34" t="n">
-        <f aca="false">IF(OR(保険一覧!$S13="",O$4&lt;保険一覧!$S13),IF(保険一覧!$J13="月払",保険一覧!$K13,IF(AND(保険一覧!$J13="年払",MONTH(O$4)=保険一覧!$R13),保険一覧!$K13,0)),0)</f>
-        <v>179573</v>
-      </c>
-      <c r="P14" s="34" t="n">
-        <f aca="false">IF(OR(保険一覧!$S13="",P$4&lt;保険一覧!$S13),IF(保険一覧!$J13="月払",保険一覧!$K13,IF(AND(保険一覧!$J13="年払",MONTH(P$4)=保険一覧!$R13),保険一覧!$K13,0)),0)</f>
-        <v>179573</v>
-      </c>
-      <c r="Q14" s="34" t="n">
-        <f aca="false">IF(OR(保険一覧!$S13="",Q$4&lt;保険一覧!$S13),IF(保険一覧!$J13="月払",保険一覧!$K13,IF(AND(保険一覧!$J13="年払",MONTH(Q$4)=保険一覧!$R13),保険一覧!$K13,0)),0)</f>
-        <v>179573</v>
-      </c>
-      <c r="R14" s="34" t="n">
-        <f aca="false">IF(OR(保険一覧!$S13="",R$4&lt;保険一覧!$S13),IF(保険一覧!$J13="月払",保険一覧!$K13,IF(AND(保険一覧!$J13="年払",MONTH(R$4)=保険一覧!$R13),保険一覧!$K13,0)),0)</f>
-        <v>179573</v>
-      </c>
-      <c r="S14" s="34" t="n">
-        <f aca="false">IF(OR(保険一覧!$S13="",S$4&lt;保険一覧!$S13),IF(保険一覧!$J13="月払",保険一覧!$K13,IF(AND(保険一覧!$J13="年払",MONTH(S$4)=保険一覧!$R13),保険一覧!$K13,0)),0)</f>
-        <v>179573</v>
-      </c>
-      <c r="T14" s="34" t="n">
-        <f aca="false">IF(OR(保険一覧!$S13="",T$4&lt;保険一覧!$S13),IF(保険一覧!$J13="月払",保険一覧!$K13,IF(AND(保険一覧!$J13="年払",MONTH(T$4)=保険一覧!$R13),保険一覧!$K13,0)),0)</f>
-        <v>179573</v>
-      </c>
-      <c r="U14" s="10" t="n">
-        <f aca="false">SUM(C14:T14)</f>
-        <v>3232314</v>
-      </c>
-      <c r="V14" s="10" t="n">
-        <f aca="false">SUMIFS(C14:T14,$C$4:$T$4,"&gt;="&amp;DATE(2027,4,1),$C$4:$T$4,"&lt;="&amp;DATE(2028,3,1))</f>
+      <c r="O14" s="10" t="n">
+        <f aca="false">SUM(C14:N14)</f>
+        <v>2154876</v>
+      </c>
+      <c r="P14" s="10" t="n">
+        <f aca="false">SUMIFS(C14:N14,$C$4:$N$4,"&gt;="&amp;DATE(2026,10,1),$C$4:$N$4,"&lt;="&amp;DATE(2027,9,1))</f>
         <v>2154876</v>
       </c>
     </row>
@@ -8115,36 +7854,12 @@
         <f aca="false">IF(OR(保険一覧!$S14="",N$4&lt;保険一覧!$S14),IF(保険一覧!$J14="月払",保険一覧!$K14,IF(AND(保険一覧!$J14="年払",MONTH(N$4)=保険一覧!$R14),保険一覧!$K14,0)),0)</f>
         <v>49628</v>
       </c>
-      <c r="O15" s="34" t="n">
-        <f aca="false">IF(OR(保険一覧!$S14="",O$4&lt;保険一覧!$S14),IF(保険一覧!$J14="月払",保険一覧!$K14,IF(AND(保険一覧!$J14="年払",MONTH(O$4)=保険一覧!$R14),保険一覧!$K14,0)),0)</f>
-        <v>49628</v>
-      </c>
-      <c r="P15" s="34" t="n">
-        <f aca="false">IF(OR(保険一覧!$S14="",P$4&lt;保険一覧!$S14),IF(保険一覧!$J14="月払",保険一覧!$K14,IF(AND(保険一覧!$J14="年払",MONTH(P$4)=保険一覧!$R14),保険一覧!$K14,0)),0)</f>
-        <v>49628</v>
-      </c>
-      <c r="Q15" s="34" t="n">
-        <f aca="false">IF(OR(保険一覧!$S14="",Q$4&lt;保険一覧!$S14),IF(保険一覧!$J14="月払",保険一覧!$K14,IF(AND(保険一覧!$J14="年払",MONTH(Q$4)=保険一覧!$R14),保険一覧!$K14,0)),0)</f>
-        <v>49628</v>
-      </c>
-      <c r="R15" s="34" t="n">
-        <f aca="false">IF(OR(保険一覧!$S14="",R$4&lt;保険一覧!$S14),IF(保険一覧!$J14="月払",保険一覧!$K14,IF(AND(保険一覧!$J14="年払",MONTH(R$4)=保険一覧!$R14),保険一覧!$K14,0)),0)</f>
-        <v>49628</v>
-      </c>
-      <c r="S15" s="34" t="n">
-        <f aca="false">IF(OR(保険一覧!$S14="",S$4&lt;保険一覧!$S14),IF(保険一覧!$J14="月払",保険一覧!$K14,IF(AND(保険一覧!$J14="年払",MONTH(S$4)=保険一覧!$R14),保険一覧!$K14,0)),0)</f>
-        <v>49628</v>
-      </c>
-      <c r="T15" s="34" t="n">
-        <f aca="false">IF(OR(保険一覧!$S14="",T$4&lt;保険一覧!$S14),IF(保険一覧!$J14="月払",保険一覧!$K14,IF(AND(保険一覧!$J14="年払",MONTH(T$4)=保険一覧!$R14),保険一覧!$K14,0)),0)</f>
-        <v>49628</v>
-      </c>
-      <c r="U15" s="10" t="n">
-        <f aca="false">SUM(C15:T15)</f>
-        <v>893304</v>
-      </c>
-      <c r="V15" s="10" t="n">
-        <f aca="false">SUMIFS(C15:T15,$C$4:$T$4,"&gt;="&amp;DATE(2027,4,1),$C$4:$T$4,"&lt;="&amp;DATE(2028,3,1))</f>
+      <c r="O15" s="10" t="n">
+        <f aca="false">SUM(C15:N15)</f>
+        <v>595536</v>
+      </c>
+      <c r="P15" s="10" t="n">
+        <f aca="false">SUMIFS(C15:N15,$C$4:$N$4,"&gt;="&amp;DATE(2026,10,1),$C$4:$N$4,"&lt;="&amp;DATE(2027,9,1))</f>
         <v>595536</v>
       </c>
     </row>
@@ -8202,36 +7917,12 @@
         <f aca="false">IF(OR(保険一覧!$S15="",N$4&lt;保険一覧!$S15),IF(保険一覧!$J15="月払",保険一覧!$K15,IF(AND(保険一覧!$J15="年払",MONTH(N$4)=保険一覧!$R15),保険一覧!$K15,0)),0)</f>
         <v>0</v>
       </c>
-      <c r="O16" s="34" t="n">
-        <f aca="false">IF(OR(保険一覧!$S15="",O$4&lt;保険一覧!$S15),IF(保険一覧!$J15="月払",保険一覧!$K15,IF(AND(保険一覧!$J15="年払",MONTH(O$4)=保険一覧!$R15),保険一覧!$K15,0)),0)</f>
-        <v>0</v>
-      </c>
-      <c r="P16" s="34" t="n">
-        <f aca="false">IF(OR(保険一覧!$S15="",P$4&lt;保険一覧!$S15),IF(保険一覧!$J15="月払",保険一覧!$K15,IF(AND(保険一覧!$J15="年払",MONTH(P$4)=保険一覧!$R15),保険一覧!$K15,0)),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q16" s="34" t="n">
-        <f aca="false">IF(OR(保険一覧!$S15="",Q$4&lt;保険一覧!$S15),IF(保険一覧!$J15="月払",保険一覧!$K15,IF(AND(保険一覧!$J15="年払",MONTH(Q$4)=保険一覧!$R15),保険一覧!$K15,0)),0)</f>
-        <v>0</v>
-      </c>
-      <c r="R16" s="34" t="n">
-        <f aca="false">IF(OR(保険一覧!$S15="",R$4&lt;保険一覧!$S15),IF(保険一覧!$J15="月払",保険一覧!$K15,IF(AND(保険一覧!$J15="年払",MONTH(R$4)=保険一覧!$R15),保険一覧!$K15,0)),0)</f>
-        <v>0</v>
-      </c>
-      <c r="S16" s="34" t="n">
-        <f aca="false">IF(OR(保険一覧!$S15="",S$4&lt;保険一覧!$S15),IF(保険一覧!$J15="月払",保険一覧!$K15,IF(AND(保険一覧!$J15="年払",MONTH(S$4)=保険一覧!$R15),保険一覧!$K15,0)),0)</f>
-        <v>0</v>
-      </c>
-      <c r="T16" s="34" t="n">
-        <f aca="false">IF(OR(保険一覧!$S15="",T$4&lt;保険一覧!$S15),IF(保険一覧!$J15="月払",保険一覧!$K15,IF(AND(保険一覧!$J15="年払",MONTH(T$4)=保険一覧!$R15),保険一覧!$K15,0)),0)</f>
-        <v>0</v>
-      </c>
-      <c r="U16" s="10" t="n">
-        <f aca="false">SUM(C16:T16)</f>
+      <c r="O16" s="10" t="n">
+        <f aca="false">SUM(C16:N16)</f>
         <v>5698547</v>
       </c>
-      <c r="V16" s="10" t="n">
-        <f aca="false">SUMIFS(C16:T16,$C$4:$T$4,"&gt;="&amp;DATE(2027,4,1),$C$4:$T$4,"&lt;="&amp;DATE(2028,3,1))</f>
+      <c r="P16" s="10" t="n">
+        <f aca="false">SUMIFS(C16:N16,$C$4:$N$4,"&gt;="&amp;DATE(2026,10,1),$C$4:$N$4,"&lt;="&amp;DATE(2027,9,1))</f>
         <v>5698547</v>
       </c>
     </row>
@@ -8289,36 +7980,12 @@
         <f aca="false">IF(OR(保険一覧!$S16="",N$4&lt;保険一覧!$S16),IF(保険一覧!$J16="月払",保険一覧!$K16,IF(AND(保険一覧!$J16="年払",MONTH(N$4)=保険一覧!$R16),保険一覧!$K16,0)),0)</f>
         <v>0</v>
       </c>
-      <c r="O17" s="34" t="n">
-        <f aca="false">IF(OR(保険一覧!$S16="",O$4&lt;保険一覧!$S16),IF(保険一覧!$J16="月払",保険一覧!$K16,IF(AND(保険一覧!$J16="年払",MONTH(O$4)=保険一覧!$R16),保険一覧!$K16,0)),0)</f>
-        <v>0</v>
-      </c>
-      <c r="P17" s="34" t="n">
-        <f aca="false">IF(OR(保険一覧!$S16="",P$4&lt;保険一覧!$S16),IF(保険一覧!$J16="月払",保険一覧!$K16,IF(AND(保険一覧!$J16="年払",MONTH(P$4)=保険一覧!$R16),保険一覧!$K16,0)),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q17" s="34" t="n">
-        <f aca="false">IF(OR(保険一覧!$S16="",Q$4&lt;保険一覧!$S16),IF(保険一覧!$J16="月払",保険一覧!$K16,IF(AND(保険一覧!$J16="年払",MONTH(Q$4)=保険一覧!$R16),保険一覧!$K16,0)),0)</f>
-        <v>0</v>
-      </c>
-      <c r="R17" s="34" t="n">
-        <f aca="false">IF(OR(保険一覧!$S16="",R$4&lt;保険一覧!$S16),IF(保険一覧!$J16="月払",保険一覧!$K16,IF(AND(保険一覧!$J16="年払",MONTH(R$4)=保険一覧!$R16),保険一覧!$K16,0)),0)</f>
-        <v>0</v>
-      </c>
-      <c r="S17" s="34" t="n">
-        <f aca="false">IF(OR(保険一覧!$S16="",S$4&lt;保険一覧!$S16),IF(保険一覧!$J16="月払",保険一覧!$K16,IF(AND(保険一覧!$J16="年払",MONTH(S$4)=保険一覧!$R16),保険一覧!$K16,0)),0)</f>
-        <v>0</v>
-      </c>
-      <c r="T17" s="34" t="n">
-        <f aca="false">IF(OR(保険一覧!$S16="",T$4&lt;保険一覧!$S16),IF(保険一覧!$J16="月払",保険一覧!$K16,IF(AND(保険一覧!$J16="年払",MONTH(T$4)=保険一覧!$R16),保険一覧!$K16,0)),0)</f>
-        <v>0</v>
-      </c>
-      <c r="U17" s="10" t="n">
-        <f aca="false">SUM(C17:T17)</f>
+      <c r="O17" s="10" t="n">
+        <f aca="false">SUM(C17:N17)</f>
         <v>1707660</v>
       </c>
-      <c r="V17" s="10" t="n">
-        <f aca="false">SUMIFS(C17:T17,$C$4:$T$4,"&gt;="&amp;DATE(2027,4,1),$C$4:$T$4,"&lt;="&amp;DATE(2028,3,1))</f>
+      <c r="P17" s="10" t="n">
+        <f aca="false">SUMIFS(C17:N17,$C$4:$N$4,"&gt;="&amp;DATE(2026,10,1),$C$4:$N$4,"&lt;="&amp;DATE(2027,9,1))</f>
         <v>1707660</v>
       </c>
     </row>
@@ -8376,36 +8043,12 @@
         <f aca="false">IF(OR(保険一覧!$S17="",N$4&lt;保険一覧!$S17),IF(保険一覧!$J17="月払",保険一覧!$K17,IF(AND(保険一覧!$J17="年払",MONTH(N$4)=保険一覧!$R17),保険一覧!$K17,0)),0)</f>
         <v>0</v>
       </c>
-      <c r="O18" s="34" t="n">
-        <f aca="false">IF(OR(保険一覧!$S17="",O$4&lt;保険一覧!$S17),IF(保険一覧!$J17="月払",保険一覧!$K17,IF(AND(保険一覧!$J17="年払",MONTH(O$4)=保険一覧!$R17),保険一覧!$K17,0)),0)</f>
-        <v>0</v>
-      </c>
-      <c r="P18" s="34" t="n">
-        <f aca="false">IF(OR(保険一覧!$S17="",P$4&lt;保険一覧!$S17),IF(保険一覧!$J17="月払",保険一覧!$K17,IF(AND(保険一覧!$J17="年払",MONTH(P$4)=保険一覧!$R17),保険一覧!$K17,0)),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q18" s="34" t="n">
-        <f aca="false">IF(OR(保険一覧!$S17="",Q$4&lt;保険一覧!$S17),IF(保険一覧!$J17="月払",保険一覧!$K17,IF(AND(保険一覧!$J17="年払",MONTH(Q$4)=保険一覧!$R17),保険一覧!$K17,0)),0)</f>
-        <v>0</v>
-      </c>
-      <c r="R18" s="34" t="n">
-        <f aca="false">IF(OR(保険一覧!$S17="",R$4&lt;保険一覧!$S17),IF(保険一覧!$J17="月払",保険一覧!$K17,IF(AND(保険一覧!$J17="年払",MONTH(R$4)=保険一覧!$R17),保険一覧!$K17,0)),0)</f>
-        <v>0</v>
-      </c>
-      <c r="S18" s="34" t="n">
-        <f aca="false">IF(OR(保険一覧!$S17="",S$4&lt;保険一覧!$S17),IF(保険一覧!$J17="月払",保険一覧!$K17,IF(AND(保険一覧!$J17="年払",MONTH(S$4)=保険一覧!$R17),保険一覧!$K17,0)),0)</f>
-        <v>0</v>
-      </c>
-      <c r="T18" s="34" t="n">
-        <f aca="false">IF(OR(保険一覧!$S17="",T$4&lt;保険一覧!$S17),IF(保険一覧!$J17="月払",保険一覧!$K17,IF(AND(保険一覧!$J17="年払",MONTH(T$4)=保険一覧!$R17),保険一覧!$K17,0)),0)</f>
-        <v>0</v>
-      </c>
-      <c r="U18" s="10" t="n">
-        <f aca="false">SUM(C18:T18)</f>
+      <c r="O18" s="10" t="n">
+        <f aca="false">SUM(C18:N18)</f>
         <v>3027080</v>
       </c>
-      <c r="V18" s="10" t="n">
-        <f aca="false">SUMIFS(C18:T18,$C$4:$T$4,"&gt;="&amp;DATE(2027,4,1),$C$4:$T$4,"&lt;="&amp;DATE(2028,3,1))</f>
+      <c r="P18" s="10" t="n">
+        <f aca="false">SUMIFS(C18:N18,$C$4:$N$4,"&gt;="&amp;DATE(2026,10,1),$C$4:$N$4,"&lt;="&amp;DATE(2027,9,1))</f>
         <v>3027080</v>
       </c>
     </row>
@@ -8463,36 +8106,12 @@
         <f aca="false">IF(OR(保険一覧!$S18="",N$4&lt;保険一覧!$S18),IF(保険一覧!$J18="月払",保険一覧!$K18,IF(AND(保険一覧!$J18="年払",MONTH(N$4)=保険一覧!$R18),保険一覧!$K18,0)),0)</f>
         <v>4973060</v>
       </c>
-      <c r="O19" s="34" t="n">
-        <f aca="false">IF(OR(保険一覧!$S18="",O$4&lt;保険一覧!$S18),IF(保険一覧!$J18="月払",保険一覧!$K18,IF(AND(保険一覧!$J18="年払",MONTH(O$4)=保険一覧!$R18),保険一覧!$K18,0)),0)</f>
-        <v>0</v>
-      </c>
-      <c r="P19" s="34" t="n">
-        <f aca="false">IF(OR(保険一覧!$S18="",P$4&lt;保険一覧!$S18),IF(保険一覧!$J18="月払",保険一覧!$K18,IF(AND(保険一覧!$J18="年払",MONTH(P$4)=保険一覧!$R18),保険一覧!$K18,0)),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q19" s="34" t="n">
-        <f aca="false">IF(OR(保険一覧!$S18="",Q$4&lt;保険一覧!$S18),IF(保険一覧!$J18="月払",保険一覧!$K18,IF(AND(保険一覧!$J18="年払",MONTH(Q$4)=保険一覧!$R18),保険一覧!$K18,0)),0)</f>
-        <v>0</v>
-      </c>
-      <c r="R19" s="34" t="n">
-        <f aca="false">IF(OR(保険一覧!$S18="",R$4&lt;保険一覧!$S18),IF(保険一覧!$J18="月払",保険一覧!$K18,IF(AND(保険一覧!$J18="年払",MONTH(R$4)=保険一覧!$R18),保険一覧!$K18,0)),0)</f>
-        <v>0</v>
-      </c>
-      <c r="S19" s="34" t="n">
-        <f aca="false">IF(OR(保険一覧!$S18="",S$4&lt;保険一覧!$S18),IF(保険一覧!$J18="月払",保険一覧!$K18,IF(AND(保険一覧!$J18="年払",MONTH(S$4)=保険一覧!$R18),保険一覧!$K18,0)),0)</f>
-        <v>0</v>
-      </c>
-      <c r="T19" s="34" t="n">
-        <f aca="false">IF(OR(保険一覧!$S18="",T$4&lt;保険一覧!$S18),IF(保険一覧!$J18="月払",保険一覧!$K18,IF(AND(保険一覧!$J18="年払",MONTH(T$4)=保険一覧!$R18),保険一覧!$K18,0)),0)</f>
-        <v>0</v>
-      </c>
-      <c r="U19" s="10" t="n">
-        <f aca="false">SUM(C19:T19)</f>
+      <c r="O19" s="10" t="n">
+        <f aca="false">SUM(C19:N19)</f>
         <v>4973060</v>
       </c>
-      <c r="V19" s="10" t="n">
-        <f aca="false">SUMIFS(C19:T19,$C$4:$T$4,"&gt;="&amp;DATE(2027,4,1),$C$4:$T$4,"&lt;="&amp;DATE(2028,3,1))</f>
+      <c r="P19" s="10" t="n">
+        <f aca="false">SUMIFS(C19:N19,$C$4:$N$4,"&gt;="&amp;DATE(2026,10,1),$C$4:$N$4,"&lt;="&amp;DATE(2027,9,1))</f>
         <v>4973060</v>
       </c>
     </row>
@@ -8550,36 +8169,12 @@
         <f aca="false">IF(OR(保険一覧!$S19="",N$4&lt;保険一覧!$S19),IF(保険一覧!$J19="月払",保険一覧!$K19,IF(AND(保険一覧!$J19="年払",MONTH(N$4)=保険一覧!$R19),保険一覧!$K19,0)),0)</f>
         <v>0</v>
       </c>
-      <c r="O20" s="34" t="n">
-        <f aca="false">IF(OR(保険一覧!$S19="",O$4&lt;保険一覧!$S19),IF(保険一覧!$J19="月払",保険一覧!$K19,IF(AND(保険一覧!$J19="年払",MONTH(O$4)=保険一覧!$R19),保険一覧!$K19,0)),0)</f>
-        <v>0</v>
-      </c>
-      <c r="P20" s="34" t="n">
-        <f aca="false">IF(OR(保険一覧!$S19="",P$4&lt;保険一覧!$S19),IF(保険一覧!$J19="月払",保険一覧!$K19,IF(AND(保険一覧!$J19="年払",MONTH(P$4)=保険一覧!$R19),保険一覧!$K19,0)),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q20" s="34" t="n">
-        <f aca="false">IF(OR(保険一覧!$S19="",Q$4&lt;保険一覧!$S19),IF(保険一覧!$J19="月払",保険一覧!$K19,IF(AND(保険一覧!$J19="年払",MONTH(Q$4)=保険一覧!$R19),保険一覧!$K19,0)),0)</f>
-        <v>0</v>
-      </c>
-      <c r="R20" s="34" t="n">
-        <f aca="false">IF(OR(保険一覧!$S19="",R$4&lt;保険一覧!$S19),IF(保険一覧!$J19="月払",保険一覧!$K19,IF(AND(保険一覧!$J19="年払",MONTH(R$4)=保険一覧!$R19),保険一覧!$K19,0)),0)</f>
-        <v>0</v>
-      </c>
-      <c r="S20" s="34" t="n">
-        <f aca="false">IF(OR(保険一覧!$S19="",S$4&lt;保険一覧!$S19),IF(保険一覧!$J19="月払",保険一覧!$K19,IF(AND(保険一覧!$J19="年払",MONTH(S$4)=保険一覧!$R19),保険一覧!$K19,0)),0)</f>
-        <v>0</v>
-      </c>
-      <c r="T20" s="34" t="n">
-        <f aca="false">IF(OR(保険一覧!$S19="",T$4&lt;保険一覧!$S19),IF(保険一覧!$J19="月払",保険一覧!$K19,IF(AND(保険一覧!$J19="年払",MONTH(T$4)=保険一覧!$R19),保険一覧!$K19,0)),0)</f>
-        <v>0</v>
-      </c>
-      <c r="U20" s="10" t="n">
-        <f aca="false">SUM(C20:T20)</f>
+      <c r="O20" s="10" t="n">
+        <f aca="false">SUM(C20:N20)</f>
         <v>3014812</v>
       </c>
-      <c r="V20" s="10" t="n">
-        <f aca="false">SUMIFS(C20:T20,$C$4:$T$4,"&gt;="&amp;DATE(2027,4,1),$C$4:$T$4,"&lt;="&amp;DATE(2028,3,1))</f>
+      <c r="P20" s="10" t="n">
+        <f aca="false">SUMIFS(C20:N20,$C$4:$N$4,"&gt;="&amp;DATE(2026,10,1),$C$4:$N$4,"&lt;="&amp;DATE(2027,9,1))</f>
         <v>3014812</v>
       </c>
     </row>
@@ -8637,36 +8232,12 @@
         <f aca="false">IF(OR(保険一覧!$S20="",N$4&lt;保険一覧!$S20),IF(保険一覧!$J20="月払",保険一覧!$K20,IF(AND(保険一覧!$J20="年払",MONTH(N$4)=保険一覧!$R20),保険一覧!$K20,0)),0)</f>
         <v>3014812</v>
       </c>
-      <c r="O21" s="34" t="n">
-        <f aca="false">IF(OR(保険一覧!$S20="",O$4&lt;保険一覧!$S20),IF(保険一覧!$J20="月払",保険一覧!$K20,IF(AND(保険一覧!$J20="年払",MONTH(O$4)=保険一覧!$R20),保険一覧!$K20,0)),0)</f>
-        <v>0</v>
-      </c>
-      <c r="P21" s="34" t="n">
-        <f aca="false">IF(OR(保険一覧!$S20="",P$4&lt;保険一覧!$S20),IF(保険一覧!$J20="月払",保険一覧!$K20,IF(AND(保険一覧!$J20="年払",MONTH(P$4)=保険一覧!$R20),保険一覧!$K20,0)),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q21" s="34" t="n">
-        <f aca="false">IF(OR(保険一覧!$S20="",Q$4&lt;保険一覧!$S20),IF(保険一覧!$J20="月払",保険一覧!$K20,IF(AND(保険一覧!$J20="年払",MONTH(Q$4)=保険一覧!$R20),保険一覧!$K20,0)),0)</f>
-        <v>0</v>
-      </c>
-      <c r="R21" s="34" t="n">
-        <f aca="false">IF(OR(保険一覧!$S20="",R$4&lt;保険一覧!$S20),IF(保険一覧!$J20="月払",保険一覧!$K20,IF(AND(保険一覧!$J20="年払",MONTH(R$4)=保険一覧!$R20),保険一覧!$K20,0)),0)</f>
-        <v>0</v>
-      </c>
-      <c r="S21" s="34" t="n">
-        <f aca="false">IF(OR(保険一覧!$S20="",S$4&lt;保険一覧!$S20),IF(保険一覧!$J20="月払",保険一覧!$K20,IF(AND(保険一覧!$J20="年払",MONTH(S$4)=保険一覧!$R20),保険一覧!$K20,0)),0)</f>
-        <v>0</v>
-      </c>
-      <c r="T21" s="34" t="n">
-        <f aca="false">IF(OR(保険一覧!$S20="",T$4&lt;保険一覧!$S20),IF(保険一覧!$J20="月払",保険一覧!$K20,IF(AND(保険一覧!$J20="年払",MONTH(T$4)=保険一覧!$R20),保険一覧!$K20,0)),0)</f>
-        <v>0</v>
-      </c>
-      <c r="U21" s="10" t="n">
-        <f aca="false">SUM(C21:T21)</f>
+      <c r="O21" s="10" t="n">
+        <f aca="false">SUM(C21:N21)</f>
         <v>3014812</v>
       </c>
-      <c r="V21" s="10" t="n">
-        <f aca="false">SUMIFS(C21:T21,$C$4:$T$4,"&gt;="&amp;DATE(2027,4,1),$C$4:$T$4,"&lt;="&amp;DATE(2028,3,1))</f>
+      <c r="P21" s="10" t="n">
+        <f aca="false">SUMIFS(C21:N21,$C$4:$N$4,"&gt;="&amp;DATE(2026,10,1),$C$4:$N$4,"&lt;="&amp;DATE(2027,9,1))</f>
         <v>3014812</v>
       </c>
     </row>
@@ -8724,36 +8295,12 @@
         <f aca="false">IF(OR(保険一覧!$S21="",N$4&lt;保険一覧!$S21),IF(保険一覧!$J21="月払",保険一覧!$K21,IF(AND(保険一覧!$J21="年払",MONTH(N$4)=保険一覧!$R21),保険一覧!$K21,0)),0)</f>
         <v>769825</v>
       </c>
-      <c r="O22" s="34" t="n">
-        <f aca="false">IF(OR(保険一覧!$S21="",O$4&lt;保険一覧!$S21),IF(保険一覧!$J21="月払",保険一覧!$K21,IF(AND(保険一覧!$J21="年払",MONTH(O$4)=保険一覧!$R21),保険一覧!$K21,0)),0)</f>
-        <v>0</v>
-      </c>
-      <c r="P22" s="34" t="n">
-        <f aca="false">IF(OR(保険一覧!$S21="",P$4&lt;保険一覧!$S21),IF(保険一覧!$J21="月払",保険一覧!$K21,IF(AND(保険一覧!$J21="年払",MONTH(P$4)=保険一覧!$R21),保険一覧!$K21,0)),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q22" s="34" t="n">
-        <f aca="false">IF(OR(保険一覧!$S21="",Q$4&lt;保険一覧!$S21),IF(保険一覧!$J21="月払",保険一覧!$K21,IF(AND(保険一覧!$J21="年払",MONTH(Q$4)=保険一覧!$R21),保険一覧!$K21,0)),0)</f>
-        <v>0</v>
-      </c>
-      <c r="R22" s="34" t="n">
-        <f aca="false">IF(OR(保険一覧!$S21="",R$4&lt;保険一覧!$S21),IF(保険一覧!$J21="月払",保険一覧!$K21,IF(AND(保険一覧!$J21="年払",MONTH(R$4)=保険一覧!$R21),保険一覧!$K21,0)),0)</f>
-        <v>0</v>
-      </c>
-      <c r="S22" s="34" t="n">
-        <f aca="false">IF(OR(保険一覧!$S21="",S$4&lt;保険一覧!$S21),IF(保険一覧!$J21="月払",保険一覧!$K21,IF(AND(保険一覧!$J21="年払",MONTH(S$4)=保険一覧!$R21),保険一覧!$K21,0)),0)</f>
-        <v>0</v>
-      </c>
-      <c r="T22" s="34" t="n">
-        <f aca="false">IF(OR(保険一覧!$S21="",T$4&lt;保険一覧!$S21),IF(保険一覧!$J21="月払",保険一覧!$K21,IF(AND(保険一覧!$J21="年払",MONTH(T$4)=保険一覧!$R21),保険一覧!$K21,0)),0)</f>
-        <v>0</v>
-      </c>
-      <c r="U22" s="10" t="n">
-        <f aca="false">SUM(C22:T22)</f>
+      <c r="O22" s="10" t="n">
+        <f aca="false">SUM(C22:N22)</f>
         <v>769825</v>
       </c>
-      <c r="V22" s="10" t="n">
-        <f aca="false">SUMIFS(C22:T22,$C$4:$T$4,"&gt;="&amp;DATE(2027,4,1),$C$4:$T$4,"&lt;="&amp;DATE(2028,3,1))</f>
+      <c r="P22" s="10" t="n">
+        <f aca="false">SUMIFS(C22:N22,$C$4:$N$4,"&gt;="&amp;DATE(2026,10,1),$C$4:$N$4,"&lt;="&amp;DATE(2027,9,1))</f>
         <v>769825</v>
       </c>
     </row>
@@ -8811,36 +8358,12 @@
         <f aca="false">IF(OR(保険一覧!$S22="",N$4&lt;保険一覧!$S22),IF(保険一覧!$J22="月払",保険一覧!$K22,IF(AND(保険一覧!$J22="年払",MONTH(N$4)=保険一覧!$R22),保険一覧!$K22,0)),0)</f>
         <v>746963</v>
       </c>
-      <c r="O23" s="34" t="n">
-        <f aca="false">IF(OR(保険一覧!$S22="",O$4&lt;保険一覧!$S22),IF(保険一覧!$J22="月払",保険一覧!$K22,IF(AND(保険一覧!$J22="年払",MONTH(O$4)=保険一覧!$R22),保険一覧!$K22,0)),0)</f>
-        <v>0</v>
-      </c>
-      <c r="P23" s="34" t="n">
-        <f aca="false">IF(OR(保険一覧!$S22="",P$4&lt;保険一覧!$S22),IF(保険一覧!$J22="月払",保険一覧!$K22,IF(AND(保険一覧!$J22="年払",MONTH(P$4)=保険一覧!$R22),保険一覧!$K22,0)),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q23" s="34" t="n">
-        <f aca="false">IF(OR(保険一覧!$S22="",Q$4&lt;保険一覧!$S22),IF(保険一覧!$J22="月払",保険一覧!$K22,IF(AND(保険一覧!$J22="年払",MONTH(Q$4)=保険一覧!$R22),保険一覧!$K22,0)),0)</f>
-        <v>0</v>
-      </c>
-      <c r="R23" s="34" t="n">
-        <f aca="false">IF(OR(保険一覧!$S22="",R$4&lt;保険一覧!$S22),IF(保険一覧!$J22="月払",保険一覧!$K22,IF(AND(保険一覧!$J22="年払",MONTH(R$4)=保険一覧!$R22),保険一覧!$K22,0)),0)</f>
-        <v>0</v>
-      </c>
-      <c r="S23" s="34" t="n">
-        <f aca="false">IF(OR(保険一覧!$S22="",S$4&lt;保険一覧!$S22),IF(保険一覧!$J22="月払",保険一覧!$K22,IF(AND(保険一覧!$J22="年払",MONTH(S$4)=保険一覧!$R22),保険一覧!$K22,0)),0)</f>
-        <v>0</v>
-      </c>
-      <c r="T23" s="34" t="n">
-        <f aca="false">IF(OR(保険一覧!$S22="",T$4&lt;保険一覧!$S22),IF(保険一覧!$J22="月払",保険一覧!$K22,IF(AND(保険一覧!$J22="年払",MONTH(T$4)=保険一覧!$R22),保険一覧!$K22,0)),0)</f>
-        <v>0</v>
-      </c>
-      <c r="U23" s="10" t="n">
-        <f aca="false">SUM(C23:T23)</f>
+      <c r="O23" s="10" t="n">
+        <f aca="false">SUM(C23:N23)</f>
         <v>746963</v>
       </c>
-      <c r="V23" s="10" t="n">
-        <f aca="false">SUMIFS(C23:T23,$C$4:$T$4,"&gt;="&amp;DATE(2027,4,1),$C$4:$T$4,"&lt;="&amp;DATE(2028,3,1))</f>
+      <c r="P23" s="10" t="n">
+        <f aca="false">SUMIFS(C23:N23,$C$4:$N$4,"&gt;="&amp;DATE(2026,10,1),$C$4:$N$4,"&lt;="&amp;DATE(2027,9,1))</f>
         <v>746963</v>
       </c>
     </row>
@@ -8898,36 +8421,12 @@
         <f aca="false">IF(OR(保険一覧!$S23="",N$4&lt;保険一覧!$S23),IF(保険一覧!$J23="月払",保険一覧!$K23,IF(AND(保険一覧!$J23="年払",MONTH(N$4)=保険一覧!$R23),保険一覧!$K23,0)),0)</f>
         <v>0</v>
       </c>
-      <c r="O24" s="34" t="n">
-        <f aca="false">IF(OR(保険一覧!$S23="",O$4&lt;保険一覧!$S23),IF(保険一覧!$J23="月払",保険一覧!$K23,IF(AND(保険一覧!$J23="年払",MONTH(O$4)=保険一覧!$R23),保険一覧!$K23,0)),0)</f>
-        <v>0</v>
-      </c>
-      <c r="P24" s="34" t="n">
-        <f aca="false">IF(OR(保険一覧!$S23="",P$4&lt;保険一覧!$S23),IF(保険一覧!$J23="月払",保険一覧!$K23,IF(AND(保険一覧!$J23="年払",MONTH(P$4)=保険一覧!$R23),保険一覧!$K23,0)),0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q24" s="34" t="n">
-        <f aca="false">IF(OR(保険一覧!$S23="",Q$4&lt;保険一覧!$S23),IF(保険一覧!$J23="月払",保険一覧!$K23,IF(AND(保険一覧!$J23="年払",MONTH(Q$4)=保険一覧!$R23),保険一覧!$K23,0)),0)</f>
-        <v>0</v>
-      </c>
-      <c r="R24" s="34" t="n">
-        <f aca="false">IF(OR(保険一覧!$S23="",R$4&lt;保険一覧!$S23),IF(保険一覧!$J23="月払",保険一覧!$K23,IF(AND(保険一覧!$J23="年払",MONTH(R$4)=保険一覧!$R23),保険一覧!$K23,0)),0)</f>
-        <v>0</v>
-      </c>
-      <c r="S24" s="34" t="n">
-        <f aca="false">IF(OR(保険一覧!$S23="",S$4&lt;保険一覧!$S23),IF(保険一覧!$J23="月払",保険一覧!$K23,IF(AND(保険一覧!$J23="年払",MONTH(S$4)=保険一覧!$R23),保険一覧!$K23,0)),0)</f>
-        <v>0</v>
-      </c>
-      <c r="T24" s="34" t="n">
-        <f aca="false">IF(OR(保険一覧!$S23="",T$4&lt;保険一覧!$S23),IF(保険一覧!$J23="月払",保険一覧!$K23,IF(AND(保険一覧!$J23="年払",MONTH(T$4)=保険一覧!$R23),保険一覧!$K23,0)),0)</f>
-        <v>0</v>
-      </c>
-      <c r="U24" s="10" t="n">
-        <f aca="false">SUM(C24:T24)</f>
-        <v>0</v>
-      </c>
-      <c r="V24" s="10" t="n">
-        <f aca="false">SUMIFS(C24:T24,$C$4:$T$4,"&gt;="&amp;DATE(2027,4,1),$C$4:$T$4,"&lt;="&amp;DATE(2028,3,1))</f>
+      <c r="O24" s="10" t="n">
+        <f aca="false">SUM(C24:N24)</f>
+        <v>0</v>
+      </c>
+      <c r="P24" s="10" t="n">
+        <f aca="false">SUMIFS(C24:N24,$C$4:$N$4,"&gt;="&amp;DATE(2026,10,1),$C$4:$N$4,"&lt;="&amp;DATE(2027,9,1))</f>
         <v>0</v>
       </c>
     </row>
@@ -8985,36 +8484,12 @@
         <f aca="false">IF(OR(保険一覧!$S24="",N$4&lt;保険一覧!$S24),IF(保険一覧!$J24="月払",保険一覧!$K24,IF(AND(保険一覧!$J24="年払",MONTH(N$4)=保険一覧!$R24),保険一覧!$K24,0)),0)</f>
         <v>28900</v>
       </c>
-      <c r="O25" s="34" t="n">
-        <f aca="false">IF(OR(保険一覧!$S24="",O$4&lt;保険一覧!$S24),IF(保険一覧!$J24="月払",保険一覧!$K24,IF(AND(保険一覧!$J24="年払",MONTH(O$4)=保険一覧!$R24),保険一覧!$K24,0)),0)</f>
-        <v>28900</v>
-      </c>
-      <c r="P25" s="34" t="n">
-        <f aca="false">IF(OR(保険一覧!$S24="",P$4&lt;保険一覧!$S24),IF(保険一覧!$J24="月払",保険一覧!$K24,IF(AND(保険一覧!$J24="年払",MONTH(P$4)=保険一覧!$R24),保険一覧!$K24,0)),0)</f>
-        <v>28900</v>
-      </c>
-      <c r="Q25" s="34" t="n">
-        <f aca="false">IF(OR(保険一覧!$S24="",Q$4&lt;保険一覧!$S24),IF(保険一覧!$J24="月払",保険一覧!$K24,IF(AND(保険一覧!$J24="年払",MONTH(Q$4)=保険一覧!$R24),保険一覧!$K24,0)),0)</f>
-        <v>28900</v>
-      </c>
-      <c r="R25" s="34" t="n">
-        <f aca="false">IF(OR(保険一覧!$S24="",R$4&lt;保険一覧!$S24),IF(保険一覧!$J24="月払",保険一覧!$K24,IF(AND(保険一覧!$J24="年払",MONTH(R$4)=保険一覧!$R24),保険一覧!$K24,0)),0)</f>
-        <v>28900</v>
-      </c>
-      <c r="S25" s="34" t="n">
-        <f aca="false">IF(OR(保険一覧!$S24="",S$4&lt;保険一覧!$S24),IF(保険一覧!$J24="月払",保険一覧!$K24,IF(AND(保険一覧!$J24="年払",MONTH(S$4)=保険一覧!$R24),保険一覧!$K24,0)),0)</f>
-        <v>28900</v>
-      </c>
-      <c r="T25" s="34" t="n">
-        <f aca="false">IF(OR(保険一覧!$S24="",T$4&lt;保険一覧!$S24),IF(保険一覧!$J24="月払",保険一覧!$K24,IF(AND(保険一覧!$J24="年払",MONTH(T$4)=保険一覧!$R24),保険一覧!$K24,0)),0)</f>
-        <v>28900</v>
-      </c>
-      <c r="U25" s="10" t="n">
-        <f aca="false">SUM(C25:T25)</f>
-        <v>520200</v>
-      </c>
-      <c r="V25" s="10" t="n">
-        <f aca="false">SUMIFS(C25:T25,$C$4:$T$4,"&gt;="&amp;DATE(2027,4,1),$C$4:$T$4,"&lt;="&amp;DATE(2028,3,1))</f>
+      <c r="O25" s="10" t="n">
+        <f aca="false">SUM(C25:N25)</f>
+        <v>346800</v>
+      </c>
+      <c r="P25" s="10" t="n">
+        <f aca="false">SUMIFS(C25:N25,$C$4:$N$4,"&gt;="&amp;DATE(2026,10,1),$C$4:$N$4,"&lt;="&amp;DATE(2027,9,1))</f>
         <v>346800</v>
       </c>
     </row>
@@ -9073,34 +8548,10 @@
       </c>
       <c r="O26" s="18" t="n">
         <f aca="false">SUM(O6:O25)</f>
-        <v>892858</v>
+        <v>33667055</v>
       </c>
       <c r="P26" s="18" t="n">
         <f aca="false">SUM(P6:P25)</f>
-        <v>892858</v>
-      </c>
-      <c r="Q26" s="18" t="n">
-        <f aca="false">SUM(Q6:Q25)</f>
-        <v>892858</v>
-      </c>
-      <c r="R26" s="18" t="n">
-        <f aca="false">SUM(R6:R25)</f>
-        <v>892858</v>
-      </c>
-      <c r="S26" s="18" t="n">
-        <f aca="false">SUM(S6:S25)</f>
-        <v>892858</v>
-      </c>
-      <c r="T26" s="18" t="n">
-        <f aca="false">SUM(T6:T25)</f>
-        <v>892858</v>
-      </c>
-      <c r="U26" s="18" t="n">
-        <f aca="false">SUM(U6:U25)</f>
-        <v>39024203</v>
-      </c>
-      <c r="V26" s="18" t="n">
-        <f aca="false">SUM(V6:V25)</f>
         <v>33667055</v>
       </c>
     </row>
